--- a/data/trans_dic/IP21-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,16</t>
+          <t>0,65; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,73; 6,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,64</t>
+          <t>0,94; 8,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,58</t>
+          <t>1,46; 7,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,01</t>
+          <t>1,44; 8,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,47</t>
+          <t>1,41; 5,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,61</t>
+          <t>1,18; 5,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,6</t>
+          <t>0,69; 5,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,72</t>
+          <t>2,71; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,67</t>
+          <t>3,56; 6,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,97</t>
+          <t>1,58; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,33</t>
+          <t>0,6; 2,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,99</t>
+          <t>3,71; 6,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,19</t>
+          <t>3,12; 6,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,51</t>
+          <t>1,89; 4,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,66</t>
+          <t>0,75; 2,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,93</t>
+          <t>3,59; 5,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,88</t>
+          <t>3,61; 5,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,75</t>
+          <t>1,99; 3,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,06</t>
+          <t>0,87; 2,11</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,77</t>
+          <t>1,86; 6,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,59</t>
+          <t>1,19; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,23</t>
+          <t>2,14; 7,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,49</t>
+          <t>0,99; 5,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,19</t>
+          <t>1,3; 6,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,18</t>
+          <t>2,35; 8,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,87</t>
+          <t>1,33; 5,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,73</t>
+          <t>0,32; 3,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,73</t>
+          <t>2,14; 5,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,75</t>
+          <t>2,16; 5,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,31</t>
+          <t>2,09; 5,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,55</t>
+          <t>1,01; 3,52</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,03</t>
+          <t>2,7; 4,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,43</t>
+          <t>2,94; 5,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,2</t>
+          <t>2,12; 4,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,24</t>
+          <t>0,77; 2,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,09</t>
+          <t>3,5; 5,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,05</t>
+          <t>3,26; 5,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,02</t>
+          <t>1,9; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,66</t>
+          <t>0,98; 2,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,04</t>
+          <t>3,39; 5,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,21</t>
+          <t>3,44; 5,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,64</t>
+          <t>2,27; 3,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,18</t>
+          <t>1,03; 2,15</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5297</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>590; 4347</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>676; 5820</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>560; 5140</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1265; 6883</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1242; 7266</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4943</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 7926</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2513; 9703</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2106; 9875</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>884; 7125</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 9416</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16975</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22212</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5462</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22106</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7757</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>41479</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44317</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26797</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13219</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>11275; 24342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16080; 31105</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7449; 18168</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2758; 10868</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>17683; 32860</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15374; 30971</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9241; 23028</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3881; 13927</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>32029; 52498</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>34114; 55101</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19119; 35881</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8487; 20639</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6618</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7200</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11916</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12340</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6343</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3233; 11429</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1991; 9271</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3690; 12496</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1482; 8728</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2057; 10056</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3993; 14076</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2494; 9452</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>584; 6772</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7102; 18228</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7276; 19138</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7538; 18780</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3378; 11713</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25411</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21228</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>58565</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>61926</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41925</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>21675</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18367; 34016</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20920; 38098</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14921; 29168</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5097; 15451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>25254; 41991</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>24456; 43167</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14159; 29730</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7477; 19516</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>47511; 70546</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>50198; 74783</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>32805; 53651</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14611; 30589</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Estudios-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,78</t>
+          <t>0,65; 5,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,3</t>
+          <t>0,72; 5,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,66</t>
+          <t>0,94; 9,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,93</t>
+          <t>1,49; 8,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,43</t>
+          <t>1,31; 7,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 12,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,46</t>
+          <t>1,39; 5,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,53</t>
+          <t>1,19; 5,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,57</t>
+          <t>0,52; 4,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,85</t>
+          <t>2,71; 5,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,88</t>
+          <t>3,5; 6,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,86</t>
+          <t>1,65; 3,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,37</t>
+          <t>0,57; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,89</t>
+          <t>3,82; 6,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,28</t>
+          <t>3,16; 6,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,71</t>
+          <t>1,89; 4,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,7</t>
+          <t>0,82; 2,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,88</t>
+          <t>3,63; 5,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,83</t>
+          <t>3,72; 5,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,74</t>
+          <t>2,04; 3,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,11</t>
+          <t>0,85; 2,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,57</t>
+          <t>1,92; 6,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,56</t>
+          <t>1,17; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,24</t>
+          <t>2,16; 6,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,84</t>
+          <t>0,95; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,36</t>
+          <t>1,6; 6,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,28</t>
+          <t>2,39; 7,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,04</t>
+          <t>1,36; 5,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,69</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,49</t>
+          <t>2,16; 5,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,68</t>
+          <t>2,25; 5,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,21</t>
+          <t>2,02; 5,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,52</t>
+          <t>0,9; 3,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,99</t>
+          <t>2,66; 4,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,36</t>
+          <t>2,86; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,15</t>
+          <t>2,15; 4,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,33</t>
+          <t>0,85; 2,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,82</t>
+          <t>3,34; 5,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 5,76</t>
+          <t>3,28; 5,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,99</t>
+          <t>1,83; 3,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,56</t>
+          <t>0,97; 2,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,03</t>
+          <t>3,33; 5,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,12</t>
+          <t>3,43; 5,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,71</t>
+          <t>2,25; 3,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,15</t>
+          <t>1,06; 2,2</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>590; 4347</t>
+          <t>587; 4914</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>676; 5820</t>
+          <t>664; 5436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>560; 5140</t>
+          <t>557; 5467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1265; 6883</t>
+          <t>1290; 7343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1242; 7266</t>
+          <t>1128; 6816</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4943</t>
+          <t>0; 4056</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7926</t>
+          <t>0; 7962</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2513; 9703</t>
+          <t>2473; 9777</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2106; 9875</t>
+          <t>2118; 10117</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>884; 7125</t>
+          <t>670; 6333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9416</t>
+          <t>0; 9910</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11275; 24342</t>
+          <t>11293; 24617</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16080; 31105</t>
+          <t>15816; 31064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7449; 18168</t>
+          <t>7792; 18817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2758; 10868</t>
+          <t>2606; 10601</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17683; 32860</t>
+          <t>18238; 33103</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15374; 30971</t>
+          <t>15592; 30423</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9241; 23028</t>
+          <t>9235; 23110</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3881; 13927</t>
+          <t>4247; 12944</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32029; 52498</t>
+          <t>32404; 53289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34114; 55101</t>
+          <t>35161; 56535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19119; 35881</t>
+          <t>19604; 36614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8487; 20639</t>
+          <t>8310; 20100</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3233; 11429</t>
+          <t>3351; 11446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1991; 9271</t>
+          <t>1953; 8998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3690; 12496</t>
+          <t>3723; 12065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1482; 8728</t>
+          <t>1423; 8033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2057; 10056</t>
+          <t>2535; 9644</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3993; 14076</t>
+          <t>4056; 13394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2494; 9452</t>
+          <t>2551; 9459</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>584; 6772</t>
+          <t>572; 6891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7102; 18228</t>
+          <t>7183; 17926</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7276; 19138</t>
+          <t>7563; 19097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7538; 18780</t>
+          <t>7286; 18536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3378; 11713</t>
+          <t>2997; 11323</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18367; 34016</t>
+          <t>18081; 33917</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20920; 38098</t>
+          <t>20332; 37653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14921; 29168</t>
+          <t>15132; 29261</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5097; 15451</t>
+          <t>5663; 15402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25254; 41991</t>
+          <t>24148; 42726</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24456; 43167</t>
+          <t>24586; 44096</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14159; 29730</t>
+          <t>13633; 29319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7477; 19516</t>
+          <t>7426; 20256</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47511; 70546</t>
+          <t>46712; 71292</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50198; 74783</t>
+          <t>50039; 74723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32805; 53651</t>
+          <t>32566; 54318</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14611; 30589</t>
+          <t>15148; 31376</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,41</t>
+          <t>1,5; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,88</t>
+          <t>1,44; 8,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,21</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,35</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,65; 5,16</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,94</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,92; 8,64</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 8,45</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 7,91</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,91</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,84</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,5</t>
+          <t>1,42; 5,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,67</t>
+          <t>1,41; 5,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,95</t>
+          <t>0,54; 5,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,49</t>
+          <t>0,0; 8,58</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -857,57 +857,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,92</t>
+          <t>3,52; 6,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,87</t>
+          <t>3,0; 6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,99</t>
+          <t>1,86; 4,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,31</t>
+          <t>0,72; 2,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,94</t>
+          <t>2,73; 5,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,17</t>
+          <t>3,37; 6,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,73</t>
+          <t>1,69; 3,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,51</t>
+          <t>0,55; 2,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,97</t>
+          <t>3,64; 5,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 5,98</t>
+          <t>3,58; 5,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,81</t>
+          <t>2,05; 3,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,8%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,58</t>
+          <t>1,29; 6,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,39</t>
+          <t>2,65; 8,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,99</t>
+          <t>1,28; 4,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,37</t>
+          <t>0,38; 3,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,1</t>
+          <t>1,81; 6,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,88</t>
+          <t>0,96; 5,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,04</t>
+          <t>2,22; 7,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,82; 5,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,4</t>
+          <t>2,18; 5,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,67</t>
+          <t>2,16; 5,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,15</t>
+          <t>2,2; 5,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,4</t>
+          <t>0,93; 3,49</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,98</t>
+          <t>3,51; 6,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,29</t>
+          <t>3,42; 6,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,16</t>
+          <t>1,93; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,32</t>
+          <t>0,95; 2,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,92</t>
+          <t>2,72; 5,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,89</t>
+          <t>2,9; 5,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,94</t>
+          <t>2,16; 4,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,66</t>
+          <t>0,79; 2,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,08</t>
+          <t>3,41; 5,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,12</t>
+          <t>3,43; 5,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,75</t>
+          <t>2,22; 3,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,2</t>
+          <t>1,04; 2,2</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1818</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2115</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5170</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2059</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>587; 4914</t>
+          <t>1300; 7452</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>664; 5436</t>
+          <t>1240; 6906</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>557; 5467</t>
+          <t>0; 6509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 7573</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>588; 4688</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5483</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>548; 5131</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1290; 7343</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1128; 6816</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4056</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 7962</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2473; 9777</t>
+          <t>2520; 9726</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2118; 10117</t>
+          <t>2521; 10019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>670; 6333</t>
+          <t>690; 7162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9910</t>
+          <t>0; 8881</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24503</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22106</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16975</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>12131</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24503</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22106</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14666</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>12150</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11293; 24617</t>
+          <t>16784; 33332</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15816; 31064</t>
+          <t>14772; 30533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7792; 18817</t>
+          <t>9106; 22061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2606; 10601</t>
+          <t>3422; 12222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18238; 33103</t>
+          <t>11360; 23815</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15592; 30423</t>
+          <t>15241; 30151</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9235; 23110</t>
+          <t>7953; 18704</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4247; 12944</t>
+          <t>2371; 9969</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32404; 53289</t>
+          <t>32547; 53002</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35161; 56535</t>
+          <t>33888; 55560</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19604; 36614</t>
+          <t>19632; 36000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8310; 20100</t>
+          <t>7666; 18655</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2292</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6618</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4377</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>7200</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5298</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7934</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5140</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5951</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3351; 11446</t>
+          <t>2033; 9790</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1953; 8998</t>
+          <t>4512; 13898</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3723; 12065</t>
+          <t>2408; 9138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1423; 8033</t>
+          <t>644; 6041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2535; 9644</t>
+          <t>3150; 11777</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4056; 13394</t>
+          <t>1607; 9325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2551; 9459</t>
+          <t>3830; 12478</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>572; 6891</t>
+          <t>1229; 7991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7183; 17926</t>
+          <t>7235; 19042</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7563; 19097</t>
+          <t>7262; 19358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7286; 18536</t>
+          <t>7923; 19123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2997; 11323</t>
+          <t>2972; 11107</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18081; 33917</t>
+          <t>25372; 43983</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20332; 37653</t>
+          <t>25642; 45340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15132; 29261</t>
+          <t>14379; 29947</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5663; 15402</t>
+          <t>6636; 18992</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24148; 42726</t>
+          <t>18554; 34256</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24586; 44096</t>
+          <t>20624; 38603</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13633; 29319</t>
+          <t>15183; 29522</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7426; 20256</t>
+          <t>4981; 14368</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46712; 71292</t>
+          <t>47799; 70704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50039; 74723</t>
+          <t>50058; 76052</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32566; 54318</t>
+          <t>32181; 52655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15148; 31376</t>
+          <t>13799; 29189</t>
         </is>
       </c>
     </row>
